--- a/artfynd/A 17736-2026 artfynd.xlsx
+++ b/artfynd/A 17736-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133427298</v>
       </c>
       <c r="B2" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133427694</v>
       </c>
       <c r="B3" t="n">
-        <v>58502</v>
+        <v>58509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133427695</v>
       </c>
       <c r="B4" t="n">
-        <v>58641</v>
+        <v>58648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>133426615</v>
       </c>
       <c r="B5" t="n">
-        <v>8444</v>
+        <v>8449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17736-2026 artfynd.xlsx
+++ b/artfynd/A 17736-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133427298</v>
       </c>
       <c r="B2" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>133427694</v>
       </c>
       <c r="B3" t="n">
-        <v>58509</v>
+        <v>58519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>133427695</v>
       </c>
       <c r="B4" t="n">
-        <v>58648</v>
+        <v>58658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 17736-2026 artfynd.xlsx
+++ b/artfynd/A 17736-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133427298</v>
+        <v>133427694</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>58519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502644</v>
+        <v>502618</v>
       </c>
       <c r="R2" t="n">
-        <v>6504513</v>
+        <v>6504490</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,32 +794,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133427694</v>
+        <v>133427298</v>
       </c>
       <c r="B3" t="n">
-        <v>58519</v>
+        <v>58136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502618</v>
+        <v>502644</v>
       </c>
       <c r="R3" t="n">
-        <v>6504490</v>
+        <v>6504513</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
